--- a/output/pdf_financials_xlsx/GCP.xlsx
+++ b/output/pdf_financials_xlsx/GCP.xlsx
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.164848</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.164848</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.241609</v>
       </c>
     </row>
     <row r="93">
@@ -3081,7 +3081,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.164848</v>
       </c>

--- a/output/pdf_financials_xlsx/GCP.xlsx
+++ b/output/pdf_financials_xlsx/GCP.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003994</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002689</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.006491</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.003994</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002689</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.006491</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.023857</v>
+        <v>0.019863</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.298602</v>
+        <v>0.295913</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.048287</v>
+        <v>0.041796</v>
       </c>
     </row>
     <row r="49">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
